--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487826_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487826_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1471</v>
+        <v>3.1773</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9084</v>
+        <v>2.8504</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7613</v>
+        <v>0.3269</v>
       </c>
       <c r="G2" t="n">
-        <v>0.819</v>
+        <v>2.4653</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9216</v>
+        <v>2.3796</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7406</v>
+        <v>0.0857</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8931</v>
+        <v>2.5104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0503</v>
+        <v>2.1063</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8428</v>
+        <v>0.4041</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.074</v>
+        <v>-0.0451</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9719</v>
+        <v>0.2733</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1022</v>
+        <v>-0.3184</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6225</v>
+        <v>-0.2337</v>
       </c>
       <c r="T2" t="n">
-        <v>1.826</v>
+        <v>0.11</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2035</v>
+        <v>-0.3438</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1675</v>
+        <v>0.1132</v>
       </c>
       <c r="W2" t="n">
         <v>0.23</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3975</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5302</v>
+        <v>2.4486</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4903</v>
+        <v>1.5556</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0399</v>
+        <v>0.8931</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4764</v>
@@ -688,13 +688,13 @@
         <v>3.1218</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2284</v>
+        <v>-0.3099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1363</v>
+        <v>0.2015</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3646</v>
+        <v>-0.5114</v>
       </c>
       <c r="V3" t="n">
         <v>0.1132</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2739</v>
+        <v>2.1892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0351</v>
+        <v>3.0093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2388</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4653</v>
+        <v>0.819</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3796</v>
+        <v>-0.9216</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0857</v>
+        <v>1.7406</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5104</v>
+        <v>2.8931</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1063</v>
+        <v>0.0503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4041</v>
+        <v>2.8428</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0451</v>
+        <v>-2.074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2733</v>
+        <v>-0.9719</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3184</v>
+        <v>-1.1022</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1371</v>
+        <v>0.6646</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7053</v>
+        <v>0.9268</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4318</v>
+        <v>-0.2622</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1132</v>
+        <v>-1.1675</v>
       </c>
       <c r="W4" t="n">
         <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1168</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2292</v>
+        <v>1.5919</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4861</v>
+        <v>1.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.257</v>
+        <v>0.4419</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5244</v>
+        <v>-1.5199</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4693</v>
+        <v>-0.9296</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9937</v>
+        <v>-0.5903</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1572</v>
+        <v>-0.0624</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9387</v>
+        <v>-0.6804</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0959</v>
+        <v>0.618</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6328</v>
+        <v>-1.4575</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4693</v>
+        <v>-0.2492</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1022</v>
+        <v>-1.2083</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1429</v>
+        <v>-0.0745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1396</v>
+        <v>0.0448</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0033</v>
+        <v>-0.1193</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.23</v>
+        <v>1.5213</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4599</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0049</v>
+        <v>1.4016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2694</v>
+        <v>1.6585</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7355</v>
+        <v>-0.257</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5199</v>
+        <v>1.5244</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9296</v>
+        <v>-0.4693</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5903</v>
+        <v>1.9937</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0624</v>
+        <v>2.1572</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6804</v>
+        <v>-0.9387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.618</v>
+        <v>3.0959</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4575</v>
+        <v>-0.6328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2492</v>
+        <v>0.4693</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2083</v>
+        <v>-1.1022</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6615</v>
+        <v>0.3153</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8358</v>
+        <v>0.312</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1743</v>
+        <v>0.0033</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5213</v>
+        <v>-0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3538</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9868</v>
+        <v>1.0393</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8387</v>
+        <v>0.1093</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1481</v>
+        <v>0.93</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0949</v>
+        <v>0.7519</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6956</v>
+        <v>0.2751</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3993</v>
+        <v>0.4768</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1639</v>
+        <v>0.1559</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0095</v>
+        <v>0.0384</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1544</v>
+        <v>0.1176</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.931</v>
+        <v>0.596</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6861</v>
+        <v>0.2367</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2449</v>
+        <v>0.3592</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2893</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3299</v>
+        <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1392</v>
+        <v>0.0793</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8757</v>
+        <v>-0.0467</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7365</v>
+        <v>0.1259</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3467</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8837</v>
+        <v>0.1002</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.105</v>
+        <v>-0.248</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9888</v>
+        <v>0.3483</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7519</v>
+        <v>0.1587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2751</v>
+        <v>-0.5075</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4768</v>
+        <v>0.6662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1559</v>
+        <v>-0.029</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0384</v>
+        <v>-0.6952</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1176</v>
+        <v>0.6662</v>
       </c>
       <c r="M8" t="n">
-        <v>0.596</v>
+        <v>0.1877</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2367</v>
+        <v>0.1877</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3592</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.358</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.261</v>
+        <v>-0.2191</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1847</v>
+        <v>-0.139</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0876</v>
+        <v>-0.0121</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5439</v>
+        <v>-1.5858</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4563</v>
+        <v>1.5737</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2156</v>
@@ -1156,13 +1156,13 @@
         <v>3.3299</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1207</v>
+        <v>-0.0452</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2668</v>
+        <v>0.2248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3875</v>
+        <v>-0.2701</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.095</v>
+        <v>-0.7546</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3552</v>
+        <v>-1.0686</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2602</v>
+        <v>0.314</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1587</v>
+        <v>-2.7331</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5075</v>
+        <v>-2.7698</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6662</v>
+        <v>0.0367</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.029</v>
+        <v>-1.7328</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6952</v>
+        <v>-1.8021</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6662</v>
+        <v>0.0694</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1877</v>
+        <v>-1.0004</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1877</v>
+        <v>-0.9677</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.0326</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5532</v>
+        <v>0.139</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3262</v>
+        <v>0.3072</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.227</v>
+        <v>-0.1683</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1168</v>
+        <v>0.5908</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1168</v>
+        <v>-0.8066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1604</v>
+        <v>-0.8077</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5625</v>
+        <v>-1.132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4021</v>
+        <v>0.3243</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7331</v>
+        <v>-3.0949</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7698</v>
+        <v>-1.6956</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0367</v>
+        <v>-1.3993</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7328</v>
+        <v>-2.1639</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8021</v>
+        <v>-1.0095</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0694</v>
+        <v>-1.1544</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0004</v>
+        <v>-0.931</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9677</v>
+        <v>-0.6861</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0326</v>
+        <v>-0.2449</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2893</v>
+        <v>3.3299</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2668</v>
+        <v>0.3446</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1866</v>
+        <v>0.9049</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.5604</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5908</v>
+        <v>-0.3467</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8066</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.142</v>
+        <v>-3.1505</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2872</v>
+        <v>-3.4718</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1452</v>
+        <v>0.3213</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9456</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6532</v>
+        <v>-0.6617</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8358</v>
+        <v>-0.0204</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8174</v>
+        <v>-0.6413</v>
       </c>
       <c r="V12" t="n">
         <v>0.5838</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.570799999999998</v>
+        <v>7.223199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.174199999999999</v>
+        <v>2.8269</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3966</v>
+        <v>4.3964</v>
       </c>
       <c r="G13" t="n">
         <v>-8.2662</v>
@@ -1441,13 +1441,13 @@
         <v>0.5305999999999997</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.07959999999999834</v>
+        <v>-0.07959999999999923</v>
       </c>
       <c r="K13" t="n">
         <v>-4.855499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.776000000000001</v>
+        <v>4.775999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-8.1867</v>
@@ -1468,19 +1468,19 @@
         <v>20.8119</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7925999999999997</v>
+        <v>-0.1401999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.093700000000001</v>
+        <v>2.7458</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.8862</v>
+        <v>-2.8866</v>
       </c>
       <c r="V13" t="n">
         <v>1.0613</v>
       </c>
       <c r="W13" t="n">
-        <v>6.403799999999999</v>
+        <v>6.4038</v>
       </c>
       <c r="X13" t="n">
         <v>-5.3423</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7068</v>
+        <v>4.9735</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7505</v>
+        <v>5.4484</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9563</v>
+        <v>-0.4749</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5267</v>
+        <v>4.2222</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9021</v>
+        <v>2.6335</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6246</v>
+        <v>1.5887</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5554</v>
+        <v>5.2471</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7225</v>
+        <v>2.4133</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8329</v>
+        <v>2.8338</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0287</v>
+        <v>-1.0249</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1796</v>
+        <v>0.2202</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2083</v>
+        <v>-1.245</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9606</v>
+        <v>-0.6244</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8788</v>
+        <v>0.0743</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0818</v>
+        <v>-0.6987</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4683</v>
+        <v>1.1675</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6211</v>
+        <v>4.7814</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5911</v>
+        <v>3.3575</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.97</v>
+        <v>1.4239</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2222</v>
+        <v>3.5267</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6335</v>
+        <v>2.9021</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5887</v>
+        <v>0.6246</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2471</v>
+        <v>3.5554</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4133</v>
+        <v>1.7225</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8338</v>
+        <v>1.8329</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0249</v>
+        <v>-0.0287</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2202</v>
+        <v>1.1796</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.245</v>
+        <v>-1.2083</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9768</v>
+        <v>1.0352</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>0.4858</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1939</v>
+        <v>0.5494</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1675</v>
+        <v>1.4683</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.029</v>
+        <v>1.5203</v>
       </c>
       <c r="E16" t="n">
         <v>0.3292</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6998</v>
+        <v>1.1911</v>
       </c>
       <c r="G16" t="n">
         <v>3.4797</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5245</v>
+        <v>-0.0332</v>
       </c>
       <c r="T16" t="n">
         <v>0.5153</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0399</v>
+        <v>-0.5486</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0531</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.584</v>
+        <v>0.5521</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2542</v>
+        <v>0.5041</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6702</v>
+        <v>0.048</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7733</v>
+        <v>1.8492</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1047</v>
+        <v>2.864</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3315</v>
+        <v>-1.0148</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.675</v>
+        <v>0.9922</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7534</v>
+        <v>1.5498</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>-0.5576</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0982</v>
+        <v>0.857</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3513</v>
+        <v>1.3141</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2531</v>
+        <v>-0.4572</v>
       </c>
       <c r="P17" t="n">
         <v>-0.6244</v>
@@ -1780,22 +1780,22 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6455</v>
+        <v>0.4241</v>
       </c>
       <c r="T17" t="n">
-        <v>3.0499</v>
+        <v>0.5525</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4044</v>
+        <v>-0.1284</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3361</v>
+        <v>-1.0968</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9199000000000001</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5838</v>
+        <v>-1.0968</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2885</v>
+        <v>0.102</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6875</v>
+        <v>-0.4732</v>
       </c>
       <c r="F18" t="n">
-        <v>0.399</v>
+        <v>0.5752</v>
       </c>
       <c r="G18" t="n">
         <v>1.0385</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2864</v>
+        <v>0.1041</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0254</v>
+        <v>0.1507</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3384</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0755</v>
+        <v>-0.9094</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4139</v>
+        <v>0.1992</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8492</v>
+        <v>-0.9051</v>
       </c>
       <c r="H19" t="n">
-        <v>2.864</v>
+        <v>-0.2365</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0148</v>
+        <v>-0.6686</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9922</v>
+        <v>-0.5784</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5498</v>
+        <v>0.0576</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5576</v>
+        <v>-0.636</v>
       </c>
       <c r="M19" t="n">
-        <v>0.857</v>
+        <v>-0.3267</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3141</v>
+        <v>-0.294</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4572</v>
+        <v>-0.0326</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4664</v>
+        <v>0.1949</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1239</v>
+        <v>-0.331</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5903</v>
+        <v>0.5259</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0968</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2372</v>
+        <v>-1.2313</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2309</v>
+        <v>-0.6746</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0063</v>
+        <v>-0.5567</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9051</v>
+        <v>-1.7733</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2365</v>
+        <v>-2.1047</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6686</v>
+        <v>0.3315</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5784</v>
+        <v>-1.675</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0576</v>
+        <v>-1.7534</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.636</v>
+        <v>0.0784</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3267</v>
+        <v>-0.0982</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.294</v>
+        <v>-0.3513</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0326</v>
+        <v>0.2531</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3321</v>
+        <v>0.8302</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6524</v>
+        <v>1.1211</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3204</v>
+        <v>-0.2909</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3361</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7961</v>
+        <v>-2.0706</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2757</v>
+        <v>-1.1686</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5204</v>
+        <v>-0.9021</v>
       </c>
       <c r="G21" t="n">
         <v>2.8004</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3608</v>
+        <v>0.0863</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.3054</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6275</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.427</v>
+        <v>-5.5825</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1228</v>
+        <v>-4.4798</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3043</v>
+        <v>-1.1027</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0489</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9734</v>
+        <v>-0.1288</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2643</v>
+        <v>0.3787</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7091</v>
+        <v>-0.5075</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8668</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.424300000000001</v>
+        <v>-7.4766</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0801</v>
+        <v>-6.33</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3443</v>
+        <v>-1.1466</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9232</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6145</v>
+        <v>0.3332</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3948</v>
+        <v>0.3553</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2198</v>
+        <v>-0.0221</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3892</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.570600000000001</v>
+        <v>-5.141900000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.396500000000001</v>
+        <v>-4.396399999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1743</v>
+        <v>-0.7456000000000003</v>
       </c>
       <c r="G24" t="n">
         <v>8.2662</v>
@@ -2308,7 +2308,7 @@
         <v>4.2454</v>
       </c>
       <c r="M24" t="n">
-        <v>0.07960000000000003</v>
+        <v>0.07960000000000014</v>
       </c>
       <c r="N24" t="n">
         <v>4.8557</v>
@@ -2326,13 +2326,13 @@
         <v>6.243599999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7928000000000004</v>
+        <v>2.2216</v>
       </c>
       <c r="T24" t="n">
-        <v>2.886299999999999</v>
+        <v>2.8862</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.093599999999999</v>
+        <v>-0.6647999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0615</v>
